--- a/data/trans_dic/IP1010-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1010-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastonos mentales</t>
+          <t>Menores que padecen trastonos mentales (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,01</t>
+          <t>0,36; 3,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -792,27 +793,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,27</t>
+          <t>0,14; 1,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,11</t>
+          <t>0,13; 1,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,74</t>
+          <t>0,29; 1,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,88</t>
+          <t>0,14; 0,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,01</t>
+          <t>0,22; 1,05</t>
         </is>
       </c>
     </row>
@@ -897,37 +898,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1007,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,0</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,09; 0,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,38</t>
+          <t>0,29; 1,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,77</t>
+          <t>0,22; 0,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,61</t>
+          <t>0,14; 0,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,76</t>
+          <t>0,18; 0,75</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastonos mentales (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3505</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4080</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3518</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>639; 5373</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3421</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1652</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4239</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3677</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4763</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3042</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6057</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2642</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>647; 5394</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>647; 5385</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1437; 8495</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>668; 6161</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1342; 8098</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2083; 10127</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2213</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4194</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4388</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4467</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2259</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4107</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5581</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4323</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5962</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2983</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1953; 9234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>645; 6611</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2179; 10137</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3100; 11162</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2048; 9506</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2643; 10800</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1010-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1010-Estudios-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,02</t>
+          <t>0,36; 2,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,13</t>
+          <t>0,14; 1,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,09</t>
+          <t>0,13; 1,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,74</t>
+          <t>0,3; 1,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,69</t>
+          <t>0,08; 0,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,86</t>
+          <t>0,15; 0,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,05</t>
+          <t>0,2; 0,98</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
     </row>
@@ -1008,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,06; 0,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,88</t>
+          <t>0,09; 0,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,36</t>
+          <t>0,29; 1,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,8</t>
+          <t>0,2; 0,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,65</t>
+          <t>0,14; 0,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,75</t>
+          <t>0,18; 0,7</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3229</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4080</t>
+          <t>0; 4129</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3518</t>
+          <t>0; 3119</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>639; 5373</t>
+          <t>636; 5305</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3421</t>
+          <t>0; 3641</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3042</t>
+          <t>0; 3044</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6057</t>
+          <t>0; 5774</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2642</t>
+          <t>0; 2640</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>647; 5394</t>
+          <t>647; 5637</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>647; 5385</t>
+          <t>646; 5419</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1437; 8495</t>
+          <t>1452; 8504</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>668; 6161</t>
+          <t>727; 6235</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1342; 8098</t>
+          <t>1401; 8646</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2083; 10127</t>
+          <t>1908; 9444</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2213</t>
+          <t>0; 2537</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4194</t>
+          <t>0; 3834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,22 +1657,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4388</t>
+          <t>0; 4076</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4467</t>
+          <t>0; 3941</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2259</t>
+          <t>0; 2511</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4107</t>
+          <t>0; 4050</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4323</t>
+          <t>0; 4360</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5962</t>
+          <t>443; 6428</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2983</t>
+          <t>0; 2598</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1953; 9234</t>
+          <t>1966; 9275</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>645; 6611</t>
+          <t>689; 6724</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2179; 10137</t>
+          <t>2171; 10557</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3100; 11162</t>
+          <t>2772; 11200</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2048; 9506</t>
+          <t>2072; 9577</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2643; 10800</t>
+          <t>2558; 10088</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1010-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1010-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,29 +678,29 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,55</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,72</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,29</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,75</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,73</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,99</t>
+          <t>0,36; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,14; 1,27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,13; 1,11</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,3; 1,74</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,73</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,28</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,56</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 1,18</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,1</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,74</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,7</t>
+          <t>0,07; 0,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,92</t>
+          <t>0,15; 0,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,98</t>
+          <t>0,21; 1,01</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,87</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,53</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,18</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,42</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,3</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,17</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,27; 1,28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,85</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,29; 1,38</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,64</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,91</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,37</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,27; 1,28</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,06; 1,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,42</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,8</t>
+          <t>0,19; 0,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,66</t>
+          <t>0,14; 0,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,7</t>
+          <t>0,18; 0,76</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,27 +1200,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1253,27 +1253,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1306,29 +1306,29 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3229</t>
+          <t>0; 4710</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 3110</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3901</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3119</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1336,12 +1336,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>636; 5305</t>
+          <t>637; 5346</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3641</t>
+          <t>0; 4242</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4239</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1652</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>524</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2040</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4239</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3044</t>
+          <t>647; 6036</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5774</t>
+          <t>645; 5463</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2640</t>
+          <t>1442; 8514</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>647; 5637</t>
+          <t>0; 3038</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>646; 5419</t>
+          <t>0; 5794</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1452; 8504</t>
+          <t>0; 2994</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>727; 6235</t>
+          <t>645; 6152</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1401; 8646</t>
+          <t>1375; 8324</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1908; 9444</t>
+          <t>1978; 9733</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 4533</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2537</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 4092</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3834</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>0; 2143</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4076</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3941</t>
+          <t>0; 4002</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2511</t>
+          <t>0; 2269</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4050</t>
+          <t>0; 4096</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>524</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4658</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5057</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4360</t>
+          <t>1951; 9248</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>443; 6428</t>
+          <t>650; 6367</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2598</t>
+          <t>2192; 10311</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1966; 9275</t>
+          <t>0; 4377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>689; 6724</t>
+          <t>443; 7101</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2171; 10557</t>
+          <t>0; 3127</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2772; 11200</t>
+          <t>2712; 10771</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2072; 9577</t>
+          <t>2003; 8839</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2558; 10088</t>
+          <t>2663; 11001</t>
         </is>
       </c>
     </row>
